--- a/warhammer40kGDR-main/GDRWarhammer40k/FileNemici.xlsx
+++ b/warhammer40kGDR-main/GDRWarhammer40k/FileNemici.xlsx
@@ -9,98 +9,101 @@
   <sheets>
     <sheet name="FileNemici" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
-  <si>
-    <t>grado nemico, nome, grado arma,grado armatura, vita</t>
-  </si>
-  <si>
-    <t>1,Tyranide,1,2,22</t>
-  </si>
-  <si>
-    <t>1,Tyranide,2,1,25</t>
-  </si>
-  <si>
-    <t>1,Tyranide,1,1,30</t>
-  </si>
-  <si>
-    <t>1,Tyranide,2,2,15</t>
-  </si>
-  <si>
-    <t>2,Tyranide,2,2,35</t>
-  </si>
-  <si>
-    <t>2,Tyranide,2,3,35</t>
-  </si>
-  <si>
-    <t>2,Tyranide,3,2,39</t>
-  </si>
-  <si>
-    <t>3,Tyranide,3,3,40</t>
-  </si>
-  <si>
-    <t>3,Tyranide,3,3,45</t>
-  </si>
-  <si>
-    <t>2,Necron,2,2,22</t>
-  </si>
-  <si>
-    <t>2,Necron,2,2,25</t>
-  </si>
-  <si>
-    <t>2,Necron,3,2,30</t>
-  </si>
-  <si>
-    <t>2,Necron,3,3,15</t>
-  </si>
-  <si>
-    <t>2,Necron,3,2,35</t>
-  </si>
-  <si>
-    <t>3,Necron,3,3,40</t>
-  </si>
-  <si>
-    <t>3,Necron,3,3,45</t>
-  </si>
-  <si>
-    <t>3,Necron,3,3,50</t>
-  </si>
-  <si>
-    <t>1,ChaosMarine,1,2,22</t>
-  </si>
-  <si>
-    <t>2,ChaosMarine,2,2,30</t>
-  </si>
-  <si>
-    <t>2,ChaosMarine,3,2,30</t>
-  </si>
-  <si>
-    <t>2,ChaosMarine,3,2,35</t>
-  </si>
-  <si>
-    <t>2,ChaosMarine,2,3,35</t>
-  </si>
-  <si>
-    <t>2,ChaosMarine,3,2,39</t>
-  </si>
-  <si>
-    <t>3,ChaosMarine,3,3,40</t>
-  </si>
-  <si>
-    <t>3,ChaosMarine,3,3,45</t>
-  </si>
-  <si>
-    <t>1,Tyranide,1,1,20</t>
-  </si>
-  <si>
-    <t>1,ChaosMarine,1,1,20</t>
-  </si>
-  <si>
-    <t>1,Necron,2,1,20</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+  <si>
+    <t>1,Tyranide,1,1,20,Tyranid1</t>
+  </si>
+  <si>
+    <t>1,Tyranide,1,2,22,Tyranid1</t>
+  </si>
+  <si>
+    <t>1,Tyranide,2,1,25,Tyranid1</t>
+  </si>
+  <si>
+    <t>1,Tyranide,1,1,30,Tyranid1</t>
+  </si>
+  <si>
+    <t>1,Tyranide,2,2,15,Tyranid1</t>
+  </si>
+  <si>
+    <t>2,Tyranide,2,2,35,Tyranid2</t>
+  </si>
+  <si>
+    <t>2,Tyranide,2,3,35,Tyranid2</t>
+  </si>
+  <si>
+    <t>2,Tyranide,3,2,39,Tyranid2</t>
+  </si>
+  <si>
+    <t>3,Tyranide,3,3,40,old-one-eye</t>
+  </si>
+  <si>
+    <t>3,Tyranide,3,3,45,old-one-eye</t>
+  </si>
+  <si>
+    <t>1,ChaosMarine,1,1,20,EmperorChildren1</t>
+  </si>
+  <si>
+    <t>2,ChaosMarine,3,2,30,EmperorChildren1</t>
+  </si>
+  <si>
+    <t>2,ChaosMarine,2,3,35,EmperorChildren1</t>
+  </si>
+  <si>
+    <t>1,ChaosMarine,1,2,22,ironWarrior1</t>
+  </si>
+  <si>
+    <t>2,ChaosMarine,3,2,35,ironWarrior1</t>
+  </si>
+  <si>
+    <t>2,ChaosMarine,3,2,39,ironWarrior1</t>
+  </si>
+  <si>
+    <t>2,ChaosMarine,2,2,30,KhornBerserk1</t>
+  </si>
+  <si>
+    <t>2,ChaosMarine,2,3,35,KhornBerserk1</t>
+  </si>
+  <si>
+    <t>3,ChaosMarine,3,3,40,KhornBerserk1</t>
+  </si>
+  <si>
+    <t>3,ChaosMarine,3,3,45,KhornBerserk1</t>
+  </si>
+  <si>
+    <t>1,Necron,2,1,20,NecronTier1</t>
+  </si>
+  <si>
+    <t>2,Necron,2,2,22,NecronTier2</t>
+  </si>
+  <si>
+    <t>2,Necron,2,2,25,NecronTier2</t>
+  </si>
+  <si>
+    <t>2,Necron,3,2,30,NecronTier2</t>
+  </si>
+  <si>
+    <t>2,Necron,3,3,15,NecronTier2</t>
+  </si>
+  <si>
+    <t>2,Necron,3,2,35,NecronTier2</t>
+  </si>
+  <si>
+    <t>3,Necron,3,3,40,NecronTier3</t>
+  </si>
+  <si>
+    <t>3,Necron,3,3,45,NecronTier3</t>
+  </si>
+  <si>
+    <t>3,Necron,3,3,50,NecronTier3</t>
+  </si>
+  <si>
+    <t>grado nemico, nome, grado arma,grado armatura, vita, nome file</t>
   </si>
 </sst>
 </file>
@@ -927,12 +930,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -982,102 +985,102 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
